--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63E8AB2-F813-4A75-9A19-156B8CEF50CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66589201-33A6-48C3-8279-E5EA31EE8E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -126,9 +126,6 @@
     <t>MERCADO LIBRE</t>
   </si>
   <si>
-    <t>CAMARA 130-90-15</t>
-  </si>
-  <si>
     <t>FITRO DE AIRE HONDA WEBE 110</t>
   </si>
   <si>
@@ -192,55 +189,43 @@
     <t>05 DE FEBRERO-26</t>
   </si>
   <si>
-    <t xml:space="preserve">CALAVERA DE DM200 TRASERA </t>
-  </si>
-  <si>
     <t>BANDA POWERLINK 743-20-30</t>
   </si>
   <si>
-    <t xml:space="preserve">AHOGADOR DE WS150 </t>
-  </si>
-  <si>
-    <t>KID DE PISTON FT150</t>
-  </si>
-  <si>
-    <t>BARRA DE POSAPIES FT125/150</t>
-  </si>
-  <si>
-    <t>FILTRO DE AIRE DOMINAR 400</t>
-  </si>
-  <si>
-    <t>PARADOR LATERAL DM200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEDAL DE ARRANQUE 150Z </t>
-  </si>
-  <si>
-    <t>11 DE FEBREREO-26</t>
-  </si>
-  <si>
-    <t>11 DE FEBRERO-26</t>
-  </si>
-  <si>
-    <t>DISCO DELANTERO DM200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARADOR LATERAL FT150 </t>
-  </si>
-  <si>
-    <t>NAASKI</t>
-  </si>
-  <si>
     <t xml:space="preserve">BUJIA MAESTRA PULSAR 200NS </t>
   </si>
   <si>
     <t>28 DE ENERO</t>
   </si>
   <si>
-    <t>CUBREPOLVO WS150</t>
-  </si>
-  <si>
-    <t>12 DE FEBRERO-26</t>
+    <t>MANDO DERECHO FT150</t>
+  </si>
+  <si>
+    <t>26 DE FEBRER0-26</t>
+  </si>
+  <si>
+    <t>BALANCIN SUPERIOR DE DS150</t>
+  </si>
+  <si>
+    <t>CAMARA 110-70-17</t>
+  </si>
+  <si>
+    <t>26 DE FEBRERO-26</t>
+  </si>
+  <si>
+    <t>BALERO 6202</t>
+  </si>
+  <si>
+    <t>BALERO 6302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 DE FEBRERO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATA LATERAL FZ16 </t>
+  </si>
+  <si>
+    <t>NSAKI</t>
   </si>
 </sst>
 </file>
@@ -796,10 +781,10 @@
   <sheetData>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>41</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="29"/>
@@ -822,10 +807,10 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>42</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>43</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
@@ -852,10 +837,10 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>51</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>52</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -1020,9 +1005,7 @@
         <v>26</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="G15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="L15" s="1"/>
@@ -1043,7 +1026,7 @@
         <v>29</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1076,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1091,14 +1074,14 @@
     </row>
     <row r="19" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="1"/>
@@ -1111,14 +1094,14 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
@@ -1131,14 +1114,14 @@
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -1151,14 +1134,14 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
@@ -1171,12 +1154,12 @@
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
@@ -1189,14 +1172,14 @@
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -1209,14 +1192,14 @@
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="25" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -1229,14 +1212,14 @@
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -1249,14 +1232,12 @@
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>2</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C27" s="7"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
@@ -1268,13 +1249,15 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8" t="s">
-        <v>54</v>
+      <c r="B28" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
@@ -1285,46 +1268,42 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="7" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8" t="s">
-        <v>54</v>
+      <c r="D29" s="18"/>
+      <c r="E29" s="22" t="s">
+        <v>58</v>
       </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8" t="s">
-        <v>54</v>
+      <c r="B30" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8" t="s">
-        <v>54</v>
+      <c r="B31" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
@@ -1332,14 +1311,12 @@
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B32" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>2</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C32" s="19"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
@@ -1347,82 +1324,58 @@
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="E34" s="1"/>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>2</v>
-      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="18"/>
-      <c r="E35" s="22" t="s">
-        <v>64</v>
-      </c>
+      <c r="E35" s="22"/>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>67</v>
-      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="E36" s="1"/>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="E37" s="1"/>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="G38" s="1"/>
@@ -1430,8 +1383,8 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="1"/>
       <c r="E39" s="8"/>
       <c r="G39" s="1"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66589201-33A6-48C3-8279-E5EA31EE8E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8CFB31-AFF1-439A-A8BE-8B172C4CAFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -150,12 +150,6 @@
     <t>Fecha</t>
   </si>
   <si>
-    <t>ACEITE MOTUL 7100-10-W40</t>
-  </si>
-  <si>
-    <t>18 DE DICIEMBRE</t>
-  </si>
-  <si>
     <t xml:space="preserve">PATITOS </t>
   </si>
   <si>
@@ -177,12 +171,6 @@
     <t>26 DE ENERO</t>
   </si>
   <si>
-    <t>ACEITE MOTUL 7100-20-50-</t>
-  </si>
-  <si>
-    <t>27 DE ENERO-26</t>
-  </si>
-  <si>
     <t>INDICADOR DE CAMBIOS FT150</t>
   </si>
   <si>
@@ -198,34 +186,58 @@
     <t>28 DE ENERO</t>
   </si>
   <si>
+    <t>26 DE FEBRERO-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATA LATERAL FZ16 </t>
+  </si>
+  <si>
+    <t>NSAKI</t>
+  </si>
+  <si>
+    <t>PEDAL DE CAMBIOS FT150</t>
+  </si>
+  <si>
+    <t>TAPA DE BACTERIA WS150 SPORT</t>
+  </si>
+  <si>
+    <t>BUJE TRASERO DM200</t>
+  </si>
+  <si>
+    <t>13 DE MARZO-26</t>
+  </si>
+  <si>
     <t>MANDO DERECHO FT150</t>
   </si>
   <si>
-    <t>26 DE FEBRER0-26</t>
-  </si>
-  <si>
-    <t>BALANCIN SUPERIOR DE DS150</t>
-  </si>
-  <si>
-    <t>CAMARA 110-70-17</t>
-  </si>
-  <si>
-    <t>26 DE FEBRERO-26</t>
-  </si>
-  <si>
-    <t>BALERO 6202</t>
-  </si>
-  <si>
-    <t>BALERO 6302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 DE FEBRERO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATA LATERAL FZ16 </t>
-  </si>
-  <si>
-    <t>NSAKI</t>
+    <t>MANDO DERECHO DM200</t>
+  </si>
+  <si>
+    <t>VALVULAS DE MOTOR DS150</t>
+  </si>
+  <si>
+    <t>19 DE MARZO-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALERO 6203 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUXILIARES BUHOS OTROS MODELOS </t>
+  </si>
+  <si>
+    <t>DIRECCIONALES DIFERENTES MODELOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 DE MARZO-26 </t>
+  </si>
+  <si>
+    <t>CHCICOTE DE CLUTH 150Z,170,250</t>
+  </si>
+  <si>
+    <t>CHICOTE DE VELOCIMETRO 125Z FT125</t>
+  </si>
+  <si>
+    <t>MANIJAS DE LUJO ROJA ,NEGRO, AZUL</t>
   </si>
 </sst>
 </file>
@@ -432,7 +444,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -440,6 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -780,7 +792,7 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="27" t="s">
@@ -806,12 +818,8 @@
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>42</v>
-      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="G6" s="1" t="s">
@@ -836,12 +844,8 @@
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>51</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="G7" s="1" t="s">
@@ -1059,7 +1063,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1114,7 +1118,7 @@
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>32</v>
@@ -1134,14 +1138,14 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24" t="s">
-        <v>44</v>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23" t="s">
+        <v>42</v>
       </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
@@ -1154,12 +1158,12 @@
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
@@ -1172,14 +1176,14 @@
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -1192,14 +1196,14 @@
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="25" t="s">
-        <v>56</v>
+      <c r="E25" s="24" t="s">
+        <v>52</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -1212,14 +1216,14 @@
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -1232,12 +1236,12 @@
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
@@ -1250,14 +1254,14 @@
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
-        <v>58</v>
+      <c r="E28" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
@@ -1268,16 +1272,16 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="20" t="s">
+    <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="22" t="s">
-        <v>58</v>
+      <c r="D29" s="1"/>
+      <c r="E29" s="25">
+        <v>46093</v>
       </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
@@ -1285,12 +1289,14 @@
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="19"/>
+        <v>57</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" s="1"/>
-      <c r="E30" s="1" t="s">
-        <v>61</v>
+      <c r="E30" s="25">
+        <v>46093</v>
       </c>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
@@ -1298,12 +1304,14 @@
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="19"/>
+        <v>58</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
@@ -1311,12 +1319,14 @@
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B32" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="19"/>
+        <v>60</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
@@ -1324,78 +1334,120 @@
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
+      <c r="B34" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="E34" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
+      <c r="B35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D35" s="18"/>
-      <c r="E35" s="22"/>
+      <c r="E35" s="21" t="s">
+        <v>63</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
+      <c r="B36" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
+      <c r="B37" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
+      <c r="B38" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
+      <c r="B39" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="8"/>
+      <c r="E39" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
+      <c r="B40" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -1440,7 +1492,7 @@
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="18"/>
-      <c r="E45" s="22"/>
+      <c r="E45" s="21"/>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -1491,7 +1543,7 @@
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="22"/>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="6"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8CFB31-AFF1-439A-A8BE-8B172C4CAFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F1D9F1-A899-491C-9272-49B2F8C2A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Gráfico1" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -153,12 +154,6 @@
     <t xml:space="preserve">PATITOS </t>
   </si>
   <si>
-    <t>24 DE ENERO</t>
-  </si>
-  <si>
-    <t>ESCAPES</t>
-  </si>
-  <si>
     <t>TAZAS DE DIRECCION RT200</t>
   </si>
   <si>
@@ -189,55 +184,94 @@
     <t>26 DE FEBRERO-26</t>
   </si>
   <si>
-    <t xml:space="preserve">PATA LATERAL FZ16 </t>
-  </si>
-  <si>
-    <t>NSAKI</t>
-  </si>
-  <si>
-    <t>PEDAL DE CAMBIOS FT150</t>
-  </si>
-  <si>
-    <t>TAPA DE BACTERIA WS150 SPORT</t>
-  </si>
-  <si>
-    <t>BUJE TRASERO DM200</t>
-  </si>
-  <si>
-    <t>13 DE MARZO-26</t>
-  </si>
-  <si>
-    <t>MANDO DERECHO FT150</t>
-  </si>
-  <si>
-    <t>MANDO DERECHO DM200</t>
-  </si>
-  <si>
-    <t>VALVULAS DE MOTOR DS150</t>
-  </si>
-  <si>
     <t>19 DE MARZO-26</t>
   </si>
   <si>
-    <t xml:space="preserve">BALERO 6203 </t>
-  </si>
-  <si>
     <t xml:space="preserve">AUXILIARES BUHOS OTROS MODELOS </t>
   </si>
   <si>
-    <t>DIRECCIONALES DIFERENTES MODELOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">20 DE MARZO-26 </t>
   </si>
   <si>
-    <t>CHCICOTE DE CLUTH 150Z,170,250</t>
-  </si>
-  <si>
-    <t>CHICOTE DE VELOCIMETRO 125Z FT125</t>
-  </si>
-  <si>
     <t>MANIJAS DE LUJO ROJA ,NEGRO, AZUL</t>
+  </si>
+  <si>
+    <t>RODILLERAS Y CODERAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCADO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSAPIES INIVERSALES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALATA DE TAMBOR CHICO VERDE </t>
+  </si>
+  <si>
+    <t>LLANTA 110-90-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSCAR </t>
+  </si>
+  <si>
+    <t>MANDO DEREHO DE 250Z</t>
+  </si>
+  <si>
+    <t>FARO DE YBR125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 DE MARZO </t>
+  </si>
+  <si>
+    <t>YUGO DE FT150</t>
+  </si>
+  <si>
+    <t>CADENA 520 CON ORING REFORZADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPEJOS DE ALERON </t>
+  </si>
+  <si>
+    <t>KID DE ARRASTRE 125Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 DE MARZO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PILA QLINK 12N7 -3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QLINK </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO AIRE DM200 ,D125.FT125 </t>
+  </si>
+  <si>
+    <t>JUNTAS DE MOTOR DM200</t>
+  </si>
+  <si>
+    <t>30 DE MARZO</t>
+  </si>
+  <si>
+    <t>ARNES H4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 DE MARZO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHIOCTE DE CLUTH 125Z </t>
+  </si>
+  <si>
+    <t>PEDAL DE ARRANQUE FT150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUBRIO FZ16 250Z . 150Z </t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 DE ABRIL </t>
+  </si>
+  <si>
+    <t>BALATA DE DSICO DS150</t>
   </si>
 </sst>
 </file>
@@ -423,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -452,6 +486,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -464,6 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,6 +515,918 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$B$40:$D$40</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>MANDO DEREHO DE 250Z</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>NASAKI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$E$14:$E$39</c:f>
+              <c:strCache>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>FECHA </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14 DE OCTUBRE </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7 DE NOVIEMBRE</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12 DE DICIEMBRE-25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17 DE DICIEMBRE </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>02 DE ENERO</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26 DE ENERO</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26 DE ENERO</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28 DE ENERO</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>05 DE FEBRERO-26</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>05 DE FEBRERO-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>26 DE FEBRERO-26</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19 DE MARZO-26</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20 DE MARZO-26 </c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20 DE MARZO-26 </c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20 DE MARZO-26 </c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20 DE MARZO-26 </c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>25/03/2026</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>25/03/2025</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25/03/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$E$40</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E402-4729-8F20-AEEC203C4F98}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1453487359"/>
+        <c:axId val="1453498399"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1453487359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1453498399"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1453498399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1453487359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{D7AE96F1-3790-47D0-BD4C-A1B099D6812F}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8664222" cy="6286500"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F82D1141-B473-64A5-267E-94E533663F0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -795,11 +1743,11 @@
       <c r="B5" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30"/>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
@@ -819,9 +1767,9 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
       <c r="G6" s="1" t="s">
         <v>4</v>
       </c>
@@ -845,9 +1793,9 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
       <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,9 +1817,9 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
       <c r="G8" s="1" t="s">
         <v>8</v>
       </c>
@@ -893,9 +1841,9 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
       <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
@@ -917,9 +1865,9 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
@@ -936,9 +1884,9 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
@@ -952,9 +1900,9 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
       <c r="G12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1063,7 +2011,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1137,16 +2085,10 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="23" t="s">
-        <v>42</v>
-      </c>
+      <c r="E22" s="23"/>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1158,12 +2100,12 @@
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
@@ -1176,14 +2118,14 @@
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -1196,14 +2138,14 @@
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -1216,14 +2158,14 @@
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -1236,12 +2178,12 @@
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
@@ -1253,15 +2195,11 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>55</v>
-      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="1"/>
       <c r="E28" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
@@ -1273,282 +2211,335 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="25">
-        <v>46093</v>
-      </c>
+      <c r="E29" s="25"/>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="25">
-        <v>46093</v>
-      </c>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="21"/>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>2</v>
+      <c r="B31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="8" t="s">
-        <v>59</v>
+      <c r="E33" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="25" t="s">
-        <v>59</v>
+      <c r="E34" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="21" t="s">
-        <v>63</v>
+    <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>32</v>
+      <c r="B36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="D36" s="1"/>
-      <c r="E36" s="1" t="s">
-        <v>63</v>
+      <c r="E36" s="25">
+        <v>46106</v>
       </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="7" t="s">
+      <c r="B37" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>67</v>
+      <c r="E37" s="25">
+        <v>45741</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="B38" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="1" t="s">
-        <v>67</v>
+      <c r="E38" s="25">
+        <v>46106</v>
       </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>2</v>
+      <c r="B39" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="8" t="s">
-        <v>67</v>
-      </c>
+      <c r="E39" s="1"/>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>67</v>
-      </c>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="18"/>
+      <c r="E40" s="21"/>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
+      <c r="B41" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="E41" s="25" t="s">
+        <v>64</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
+      <c r="B42" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="E42" s="25" t="s">
+        <v>64</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
+      <c r="B43" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
+      <c r="E43" s="25" t="s">
+        <v>64</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
+      <c r="B44" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>5</v>
+      </c>
       <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>2</v>
+      </c>
       <c r="D45" s="18"/>
-      <c r="E45" s="21"/>
+      <c r="E45" s="21" t="s">
+        <v>69</v>
+      </c>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
+      <c r="B46" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>71</v>
+      </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
+      <c r="B47" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
+      <c r="B48" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="49" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
+      <c r="B49" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="50" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
+      <c r="B50" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="51" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
+      <c r="B51" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
+      <c r="B52" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>2</v>
+      </c>
       <c r="D52" s="18"/>
-      <c r="E52" s="21"/>
+      <c r="E52" s="21" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="53" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
+      <c r="B53" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="D53" s="1"/>
+      <c r="E53" s="31" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="54" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="6"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F1D9F1-A899-491C-9272-49B2F8C2A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F7B5C-F6DA-40D5-9E25-3D1545EC3A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -154,9 +154,6 @@
     <t xml:space="preserve">PATITOS </t>
   </si>
   <si>
-    <t>TAZAS DE DIRECCION RT200</t>
-  </si>
-  <si>
     <t>ASAKI</t>
   </si>
   <si>
@@ -172,18 +169,12 @@
     <t>05 DE FEBRERO-26</t>
   </si>
   <si>
-    <t>BANDA POWERLINK 743-20-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">BUJIA MAESTRA PULSAR 200NS </t>
   </si>
   <si>
     <t>28 DE ENERO</t>
   </si>
   <si>
-    <t>26 DE FEBRERO-26</t>
-  </si>
-  <si>
     <t>19 DE MARZO-26</t>
   </si>
   <si>
@@ -202,33 +193,12 @@
     <t xml:space="preserve">MERCADO </t>
   </si>
   <si>
-    <t xml:space="preserve">POSAPIES INIVERSALES </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BALATA DE TAMBOR CHICO VERDE </t>
-  </si>
-  <si>
-    <t>LLANTA 110-90-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSCAR </t>
-  </si>
-  <si>
-    <t>MANDO DEREHO DE 250Z</t>
-  </si>
-  <si>
-    <t>FARO DE YBR125</t>
-  </si>
-  <si>
     <t xml:space="preserve">26 DE MARZO </t>
   </si>
   <si>
     <t>YUGO DE FT150</t>
   </si>
   <si>
-    <t>CADENA 520 CON ORING REFORZADA</t>
-  </si>
-  <si>
     <t xml:space="preserve">ESPEJOS DE ALERON </t>
   </si>
   <si>
@@ -238,15 +208,6 @@
     <t xml:space="preserve">27 DE MARZO </t>
   </si>
   <si>
-    <t xml:space="preserve">PILA QLINK 12N7 -3B </t>
-  </si>
-  <si>
-    <t xml:space="preserve">QLINK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO AIRE DM200 ,D125.FT125 </t>
-  </si>
-  <si>
     <t>JUNTAS DE MOTOR DM200</t>
   </si>
   <si>
@@ -272,6 +233,48 @@
   </si>
   <si>
     <t>BALATA DE DSICO DS150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALARMA PARA MOTO </t>
+  </si>
+  <si>
+    <t>06 DE ABRIL</t>
+  </si>
+  <si>
+    <t>SWUITH DS150</t>
+  </si>
+  <si>
+    <t>ARNES DE DM200</t>
+  </si>
+  <si>
+    <t>PARADOR LATERAL DE YB R125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NASAKI </t>
+  </si>
+  <si>
+    <t>CARGADOR DE CELULAR</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>NASAKIK</t>
+  </si>
+  <si>
+    <t>26 DE MARZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICOTED E VELOCIMETRO WS150 </t>
+  </si>
+  <si>
+    <t>10 DE ABRIL-26</t>
+  </si>
+  <si>
+    <t>CHCICOTE DE ACELERADOR WS150 SPORT</t>
+  </si>
+  <si>
+    <t>FILTROS DE ALTO FLUJO</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>MANDO DEREHO DE 250Z</c:v>
+                  <c:v>SWUITH DS150</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>NASAKI</c:v>
@@ -599,7 +602,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -618,9 +621,6 @@
                 <c:pt idx="7">
                   <c:v>02 DE ENERO</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>26 DE ENERO</c:v>
-                </c:pt>
                 <c:pt idx="10">
                   <c:v>26 DE ENERO</c:v>
                 </c:pt>
@@ -631,34 +631,43 @@
                   <c:v>05 DE FEBRERO-26</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>05 DE FEBRERO-26</c:v>
+                  <c:v>19 DE MARZO-26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>26 DE FEBRERO-26</c:v>
+                  <c:v>20 DE MARZO-26 </c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>25/03/2026</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26 DE MARZO</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19 DE MARZO-26</c:v>
+                  <c:v>26 DE MARZO </c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>20 DE MARZO-26 </c:v>
+                  <c:v>27 DE MARZO </c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20 DE MARZO-26 </c:v>
+                  <c:v>30 DE MARZO</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20 DE MARZO-26 </c:v>
+                  <c:v>30 DE MARZO </c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>20 DE MARZO-26 </c:v>
+                  <c:v>30 DE MARZO </c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>25/03/2026</c:v>
+                  <c:v>30 DE MARZO</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>25/03/2025</c:v>
+                  <c:v>02 DE ABRIL </c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25/03/2026</c:v>
+                  <c:v>02 DE ABRIL </c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>06 DE ABRIL</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -669,6 +678,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2011,7 +2023,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -2099,14 +2111,10 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
-        <v>45</v>
-      </c>
+      <c r="E23" s="8"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2118,14 +2126,14 @@
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -2138,14 +2146,14 @@
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -2158,14 +2166,14 @@
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -2178,12 +2186,14 @@
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
@@ -2195,10 +2205,14 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
+      <c r="B28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G28" s="1"/>
@@ -2211,68 +2225,90 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="25"/>
+      <c r="B29" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="25">
+        <v>46106</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="21"/>
+      <c r="B30" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="21" t="s">
+        <v>78</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="D31" s="8"/>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>54</v>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="22"/>
+      <c r="E32" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="1"/>
+      <c r="B33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="8"/>
       <c r="E33" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
+      <c r="B34" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="C34" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="8" t="s">
-        <v>54</v>
+      <c r="D34" s="8"/>
+      <c r="E34" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
@@ -2280,100 +2316,104 @@
     </row>
     <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="D35" s="8"/>
       <c r="E35" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="25">
-        <v>46106</v>
+      <c r="B36" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="19" t="s">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="25">
-        <v>45741</v>
+      <c r="D37" s="22"/>
+      <c r="E37" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="25">
-        <v>46106</v>
+      <c r="D38" s="8"/>
+      <c r="E38" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="B39" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="21" t="s">
+        <v>70</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="26" t="s">
+    <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="21"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="21" t="s">
+        <v>70</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="10" t="s">
-        <v>63</v>
+      <c r="B41" s="19" t="s">
+        <v>72</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D41" s="1"/>
-      <c r="E41" s="25" t="s">
-        <v>64</v>
+      <c r="E41" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
@@ -2381,29 +2421,29 @@
     </row>
     <row r="42" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="19" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D42" s="1"/>
-      <c r="E42" s="25" t="s">
-        <v>64</v>
+      <c r="E42" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>2</v>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="25" t="s">
-        <v>64</v>
+      <c r="E43" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="G43" s="1"/>
       <c r="I43" s="1"/>
@@ -2411,14 +2451,14 @@
     </row>
     <row r="44" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B44" s="19" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G44" s="1"/>
       <c r="I44" s="1"/>
@@ -2426,14 +2466,14 @@
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="26" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C45" s="26" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="21" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
@@ -2441,115 +2481,75 @@
     </row>
     <row r="46" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B46" s="19" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="G46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="E47" s="1"/>
       <c r="G47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="E48" s="1"/>
     </row>
     <row r="49" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="E49" s="1"/>
     </row>
     <row r="50" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="E50" s="1"/>
     </row>
     <row r="51" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="E51" s="1"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>2</v>
-      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="21" t="s">
-        <v>80</v>
-      </c>
+      <c r="E52" s="21"/>
     </row>
     <row r="53" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="31" t="s">
-        <v>80</v>
-      </c>
+      <c r="E53" s="21"/>
     </row>
     <row r="54" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="1"/>
+      <c r="E54" s="21"/>
     </row>
     <row r="55" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="1"/>
+      <c r="E55" s="21"/>
     </row>
     <row r="56" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B56" s="6"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F7B5C-F6DA-40D5-9E25-3D1545EC3A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAD9468-EAC9-4C62-BFE4-12030935B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -133,15 +133,6 @@
     <t>12 DE DICIEMBRE-25</t>
   </si>
   <si>
-    <t xml:space="preserve">PORTA PLACAS DE METAL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 DE DICIEMBRE </t>
-  </si>
-  <si>
-    <t>02 DE ENERO</t>
-  </si>
-  <si>
     <t xml:space="preserve">POSAPIE DE 250Z AMBOS </t>
   </si>
   <si>
@@ -157,93 +148,15 @@
     <t>ASAKI</t>
   </si>
   <si>
-    <t xml:space="preserve">BALATA DE CROSMAX TRASERA </t>
-  </si>
-  <si>
-    <t>26 DE ENERO</t>
-  </si>
-  <si>
     <t>INDICADOR DE CAMBIOS FT150</t>
   </si>
   <si>
     <t>05 DE FEBRERO-26</t>
   </si>
   <si>
-    <t xml:space="preserve">BUJIA MAESTRA PULSAR 200NS </t>
-  </si>
-  <si>
-    <t>28 DE ENERO</t>
-  </si>
-  <si>
-    <t>19 DE MARZO-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUXILIARES BUHOS OTROS MODELOS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 DE MARZO-26 </t>
-  </si>
-  <si>
-    <t>MANIJAS DE LUJO ROJA ,NEGRO, AZUL</t>
-  </si>
-  <si>
-    <t>RODILLERAS Y CODERAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MERCADO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 DE MARZO </t>
-  </si>
-  <si>
     <t>YUGO DE FT150</t>
   </si>
   <si>
-    <t xml:space="preserve">ESPEJOS DE ALERON </t>
-  </si>
-  <si>
-    <t>KID DE ARRASTRE 125Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 DE MARZO </t>
-  </si>
-  <si>
-    <t>JUNTAS DE MOTOR DM200</t>
-  </si>
-  <si>
-    <t>30 DE MARZO</t>
-  </si>
-  <si>
-    <t>ARNES H4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 DE MARZO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHIOCTE DE CLUTH 125Z </t>
-  </si>
-  <si>
-    <t>PEDAL DE ARRANQUE FT150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUBRIO FZ16 250Z . 150Z </t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 DE ABRIL </t>
-  </si>
-  <si>
-    <t>BALATA DE DSICO DS150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALARMA PARA MOTO </t>
-  </si>
-  <si>
-    <t>06 DE ABRIL</t>
-  </si>
-  <si>
-    <t>SWUITH DS150</t>
-  </si>
-  <si>
     <t>ARNES DE DM200</t>
   </si>
   <si>
@@ -259,22 +172,67 @@
     <t>OSCAR</t>
   </si>
   <si>
-    <t>NASAKIK</t>
-  </si>
-  <si>
     <t>26 DE MARZO</t>
   </si>
   <si>
-    <t xml:space="preserve">CHICOTED E VELOCIMETRO WS150 </t>
-  </si>
-  <si>
     <t>10 DE ABRIL-26</t>
   </si>
   <si>
-    <t>CHCICOTE DE ACELERADOR WS150 SPORT</t>
-  </si>
-  <si>
-    <t>FILTROS DE ALTO FLUJO</t>
+    <t>AJUSTADOR DE CADENA DM200</t>
+  </si>
+  <si>
+    <t>14 DE ABRIL-26</t>
+  </si>
+  <si>
+    <t>MANUBRIO DM200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 DE ABRIL-26 </t>
+  </si>
+  <si>
+    <t>COPLE PARA MOFLE  FT125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDIDO MERCADO LIBRE </t>
+  </si>
+  <si>
+    <t>FILTRO DE GASOLINA CARTON</t>
+  </si>
+  <si>
+    <t>NASAKI WAPEMEX</t>
+  </si>
+  <si>
+    <t>AJUSTADOR DE LA 125Z</t>
+  </si>
+  <si>
+    <t>KID DE CILINDRO DS150</t>
+  </si>
+  <si>
+    <t>16 DE ABRIL-26</t>
+  </si>
+  <si>
+    <t>POSAPIE IZQUIERO DERECHO 250Z Y IZQUIERDO 250Z</t>
+  </si>
+  <si>
+    <t>POPOTE PARA RIND ROJO</t>
+  </si>
+  <si>
+    <t>22 DE ABRIL-26</t>
+  </si>
+  <si>
+    <t>EJE TRASERO FT150</t>
+  </si>
+  <si>
+    <t>PEDAL DE ARRANUQE DM200</t>
+  </si>
+  <si>
+    <t>25 DE ABRIL-26</t>
+  </si>
+  <si>
+    <t>JUNTAS DE MOTOR FZ16</t>
+  </si>
+  <si>
+    <t>CAMARA 90-90-18</t>
   </si>
 </sst>
 </file>
@@ -460,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -487,9 +445,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -502,7 +457,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +534,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>SWUITH DS150</c:v>
+                  <c:v>PEDAL DE ARRANUQE DM200</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>NASAKI</c:v>
@@ -602,7 +556,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -615,59 +569,53 @@
                 <c:pt idx="5">
                   <c:v>12 DE DICIEMBRE-25</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>17 DE DICIEMBRE </c:v>
+                <c:pt idx="8">
+                  <c:v>05 DE FEBRERO-26</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>02 DE ENERO</c:v>
+                <c:pt idx="9">
+                  <c:v>26 DE MARZO</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>26 DE ENERO</c:v>
+                  <c:v>10 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>28 DE ENERO</c:v>
+                  <c:v>10 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>05 DE FEBRERO-26</c:v>
+                  <c:v>10 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>19 DE MARZO-26</c:v>
+                  <c:v>14 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20 DE MARZO-26 </c:v>
+                  <c:v>15 DE ABRIL-26 </c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25/03/2026</c:v>
+                  <c:v>15 DE ABRIL-26 </c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>26 DE MARZO</c:v>
+                  <c:v>16 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>26 DE MARZO </c:v>
+                  <c:v>16 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>27 DE MARZO </c:v>
+                  <c:v>16 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>30 DE MARZO</c:v>
+                  <c:v>22 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>30 DE MARZO </c:v>
+                  <c:v>22 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>30 DE MARZO </c:v>
+                  <c:v>25 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>30 DE MARZO</c:v>
+                  <c:v>25 DE ABRIL-26</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>02 DE ABRIL </c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>02 DE ABRIL </c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>06 DE ABRIL</c:v>
+                  <c:v>25 DE ABRIL-26</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -678,9 +626,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1745,7 +1690,7 @@
     <col min="3" max="3" width="26.7109375" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="34.85546875" customWidth="1"/>
+    <col min="7" max="7" width="55.28515625" customWidth="1"/>
     <col min="9" max="9" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5703125" customWidth="1"/>
     <col min="12" max="12" width="34.5703125" customWidth="1"/>
@@ -1753,13 +1698,13 @@
   <sheetData>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="30"/>
+        <v>36</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="27"/>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1779,9 +1724,9 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="G6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1805,9 +1750,9 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
       <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1829,9 +1774,9 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
       <c r="G8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1853,9 +1798,9 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
       <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1877,9 +1822,9 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
       <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1896,9 +1841,9 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1912,9 +1857,9 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
       <c r="G12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,7 +1968,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -2038,7 +1983,7 @@
     </row>
     <row r="19" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>32</v>
@@ -2058,15 +2003,11 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>32</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C20" s="9"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E20" s="1"/>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2077,16 +2018,10 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="15" t="s">
-        <v>37</v>
-      </c>
+      <c r="E21" s="15"/>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -2097,10 +2032,16 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="B22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
+      <c r="E22" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -2111,10 +2052,16 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2131,9 +2078,9 @@
       <c r="C24" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
-        <v>44</v>
+      <c r="D24" s="1"/>
+      <c r="E24" s="21" t="s">
+        <v>49</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -2146,14 +2093,14 @@
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="24" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="21" t="s">
+        <v>49</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -2164,16 +2111,16 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8" t="s">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
         <v>46</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="21" t="s">
+        <v>49</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -2185,15 +2132,15 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8" t="s">
-        <v>49</v>
+      <c r="C27" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
@@ -2205,15 +2152,15 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>5</v>
+      <c r="C28" s="19" t="s">
+        <v>2</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
@@ -2225,60 +2172,60 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="25">
-        <v>46106</v>
       </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="9" t="s">
+    <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21" t="s">
-        <v>78</v>
+      <c r="C30" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="8"/>
+      <c r="B31" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="9" t="s">
+    <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="21" t="s">
-        <v>59</v>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
@@ -2286,14 +2233,14 @@
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
@@ -2301,7 +2248,7 @@
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>2</v>
@@ -2316,14 +2263,14 @@
     </row>
     <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
@@ -2331,14 +2278,14 @@
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
@@ -2346,150 +2293,96 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="21" t="s">
-        <v>67</v>
-      </c>
+      <c r="E38" s="21"/>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>5</v>
-      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="21" t="s">
-        <v>70</v>
-      </c>
+      <c r="E39" s="21"/>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="21" t="s">
-        <v>70</v>
-      </c>
+      <c r="E40" s="21"/>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="31" t="s">
-        <v>80</v>
-      </c>
+      <c r="E41" s="21"/>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>74</v>
-      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="31" t="s">
-        <v>80</v>
-      </c>
+      <c r="E42" s="21"/>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>76</v>
-      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="31" t="s">
-        <v>80</v>
-      </c>
+      <c r="E43" s="21"/>
       <c r="G43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="E44" s="1"/>
       <c r="G44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>2</v>
-      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
       <c r="D45" s="18"/>
-      <c r="E45" s="21" t="s">
-        <v>80</v>
-      </c>
+      <c r="E45" s="21"/>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="E46" s="1"/>
       <c r="G46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2509,169 +2402,200 @@
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
-    <row r="49" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G49" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G51" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="21"/>
-    </row>
-    <row r="53" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="21"/>
-    </row>
-    <row r="54" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="21"/>
-    </row>
-    <row r="55" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E54" s="1"/>
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="21"/>
-    </row>
-    <row r="56" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
+      <c r="E55" s="1"/>
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
       <c r="D56" s="1"/>
-    </row>
-    <row r="57" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E56" s="1"/>
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="1"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E57" s="1"/>
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="1"/>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E58" s="1"/>
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="1"/>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E59" s="1"/>
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="1"/>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E60" s="1"/>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="1"/>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E61" s="1"/>
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="1"/>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E62" s="1"/>
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="1"/>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="1"/>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="1"/>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="1"/>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="1"/>
     </row>
-    <row r="68" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="1"/>
     </row>
-    <row r="71" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="1"/>
     </row>
-    <row r="72" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
       <c r="D72" s="1"/>
     </row>
-    <row r="73" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
       <c r="D73" s="1"/>
     </row>
-    <row r="74" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
       <c r="D74" s="1"/>
     </row>
-    <row r="75" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="1"/>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="1"/>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="1"/>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="1"/>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="1"/>
     </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="1"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAD9468-EAC9-4C62-BFE4-12030935B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4497C0-3F83-4E1D-88DF-E3F56D472351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -148,69 +148,12 @@
     <t>ASAKI</t>
   </si>
   <si>
-    <t>INDICADOR DE CAMBIOS FT150</t>
-  </si>
-  <si>
-    <t>05 DE FEBRERO-26</t>
-  </si>
-  <si>
-    <t>YUGO DE FT150</t>
-  </si>
-  <si>
     <t>ARNES DE DM200</t>
   </si>
   <si>
-    <t>PARADOR LATERAL DE YB R125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NASAKI </t>
-  </si>
-  <si>
-    <t>CARGADOR DE CELULAR</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>26 DE MARZO</t>
-  </si>
-  <si>
-    <t>10 DE ABRIL-26</t>
-  </si>
-  <si>
-    <t>AJUSTADOR DE CADENA DM200</t>
-  </si>
-  <si>
-    <t>14 DE ABRIL-26</t>
-  </si>
-  <si>
-    <t>MANUBRIO DM200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 DE ABRIL-26 </t>
-  </si>
-  <si>
-    <t>COPLE PARA MOFLE  FT125</t>
-  </si>
-  <si>
     <t xml:space="preserve">PEDIDO MERCADO LIBRE </t>
   </si>
   <si>
-    <t>FILTRO DE GASOLINA CARTON</t>
-  </si>
-  <si>
-    <t>NASAKI WAPEMEX</t>
-  </si>
-  <si>
-    <t>AJUSTADOR DE LA 125Z</t>
-  </si>
-  <si>
-    <t>KID DE CILINDRO DS150</t>
-  </si>
-  <si>
-    <t>16 DE ABRIL-26</t>
-  </si>
-  <si>
     <t>POSAPIE IZQUIERO DERECHO 250Z Y IZQUIERDO 250Z</t>
   </si>
   <si>
@@ -233,6 +176,63 @@
   </si>
   <si>
     <t>CAMARA 90-90-18</t>
+  </si>
+  <si>
+    <t>CALIPER DE ATV</t>
+  </si>
+  <si>
+    <t>PEDAL DE CAMBIOS 125Z</t>
+  </si>
+  <si>
+    <t>MANUBRIOFZ16</t>
+  </si>
+  <si>
+    <t>CHICOTED E CLUTH FT150</t>
+  </si>
+  <si>
+    <t>NASAKIK</t>
+  </si>
+  <si>
+    <t>10 DE ABRIL</t>
+  </si>
+  <si>
+    <t>PARADOR YBR125</t>
+  </si>
+  <si>
+    <t>16 DE ABRIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO DE GASOLINA CARTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAPEMEX </t>
+  </si>
+  <si>
+    <t>ARNES PRINCIPAL FT150</t>
+  </si>
+  <si>
+    <t>WAPEMEX</t>
+  </si>
+  <si>
+    <t>MANIJA IZQUIERDA BOXER 150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUBRIO DE 3 PIEZAS </t>
+  </si>
+  <si>
+    <t>FILTROD E ACEITE FZ16</t>
+  </si>
+  <si>
+    <t>ACIENTO DE 150Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSAPIE UNIVERSALES </t>
+  </si>
+  <si>
+    <t>MANIJA IZQUIERDA FT150</t>
+  </si>
+  <si>
+    <t>02 DE MAYO</t>
   </si>
 </sst>
 </file>
@@ -534,7 +534,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>PEDAL DE ARRANUQE DM200</c:v>
+                  <c:v>MANUBRIOFZ16</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>NASAKI</c:v>
@@ -569,38 +569,14 @@
                 <c:pt idx="5">
                   <c:v>12 DE DICIEMBRE-25</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>10 DE ABRIL</c:v>
+                </c:pt>
                 <c:pt idx="8">
-                  <c:v>05 DE FEBRERO-26</c:v>
+                  <c:v>16 DE ABRIL</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>26 DE MARZO</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>10 DE ABRIL-26</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10 DE ABRIL-26</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>10 DE ABRIL-26</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14 DE ABRIL-26</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15 DE ABRIL-26 </c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15 DE ABRIL-26 </c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>16 DE ABRIL-26</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>16 DE ABRIL-26</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>16 DE ABRIL-26</c:v>
+                  <c:v>16 DE ABRIL</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>22 DE ABRIL-26</c:v>
@@ -2018,10 +1994,16 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="B21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="15"/>
+      <c r="E21" s="15" t="s">
+        <v>55</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -2033,14 +2015,12 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>2</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C22" s="9"/>
       <c r="D22" s="22"/>
       <c r="E22" s="23" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
@@ -2053,14 +2033,14 @@
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
@@ -2072,16 +2052,10 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="21" t="s">
-        <v>49</v>
-      </c>
+      <c r="E24" s="21"/>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -2092,16 +2066,10 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="21" t="s">
-        <v>49</v>
-      </c>
+      <c r="E25" s="21"/>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2112,16 +2080,10 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="21" t="s">
-        <v>49</v>
-      </c>
+      <c r="E26" s="21"/>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2132,16 +2094,10 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="E27" s="1"/>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2152,16 +2108,10 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="19"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2172,75 +2122,51 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="E29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>57</v>
-      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="E30" s="1"/>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="E31" s="1"/>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="E32" s="1"/>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="8" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
@@ -2248,14 +2174,14 @@
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
@@ -2263,14 +2189,14 @@
     </row>
     <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
@@ -2278,14 +2204,14 @@
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
@@ -2293,22 +2219,26 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="21" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
+      <c r="B38" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D38" s="8"/>
       <c r="E38" s="21"/>
       <c r="G38" s="1"/>
@@ -2316,8 +2246,12 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
+      <c r="B39" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" s="8"/>
       <c r="E39" s="21"/>
       <c r="G39" s="1"/>
@@ -2325,8 +2259,12 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
+      <c r="B40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D40" s="8"/>
       <c r="E40" s="21"/>
       <c r="G40" s="1"/>
@@ -2334,8 +2272,12 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
+      <c r="B41" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="21"/>
       <c r="G41" s="1"/>
@@ -2343,17 +2285,27 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
+      <c r="B42" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="D42" s="1"/>
-      <c r="E42" s="21"/>
+      <c r="E42" s="21" t="s">
+        <v>68</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="21"/>
       <c r="G43" s="1"/>
@@ -2361,8 +2313,12 @@
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
+      <c r="B44" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="G44" s="1"/>
@@ -2370,8 +2326,12 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D45" s="18"/>
       <c r="E45" s="21"/>
       <c r="G45" s="1"/>
@@ -2379,8 +2339,12 @@
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
+      <c r="B46" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="G46" s="1"/>
@@ -2388,8 +2352,12 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
+      <c r="B47" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="G47" s="1"/>
@@ -2397,8 +2365,12 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
+      <c r="B48" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
@@ -2408,7 +2380,7 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="G49" s="10" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2426,7 +2398,7 @@
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="G51" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4497C0-3F83-4E1D-88DF-E3F56D472351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1270C95B-320A-4236-88A9-2CCA2D22F42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -148,27 +148,12 @@
     <t>ASAKI</t>
   </si>
   <si>
-    <t>ARNES DE DM200</t>
-  </si>
-  <si>
     <t xml:space="preserve">PEDIDO MERCADO LIBRE </t>
   </si>
   <si>
     <t>POSAPIE IZQUIERO DERECHO 250Z Y IZQUIERDO 250Z</t>
   </si>
   <si>
-    <t>POPOTE PARA RIND ROJO</t>
-  </si>
-  <si>
-    <t>22 DE ABRIL-26</t>
-  </si>
-  <si>
-    <t>EJE TRASERO FT150</t>
-  </si>
-  <si>
-    <t>PEDAL DE ARRANUQE DM200</t>
-  </si>
-  <si>
     <t>25 DE ABRIL-26</t>
   </si>
   <si>
@@ -178,9 +163,6 @@
     <t>CAMARA 90-90-18</t>
   </si>
   <si>
-    <t>CALIPER DE ATV</t>
-  </si>
-  <si>
     <t>PEDAL DE CAMBIOS 125Z</t>
   </si>
   <si>
@@ -190,24 +172,12 @@
     <t>CHICOTED E CLUTH FT150</t>
   </si>
   <si>
-    <t>NASAKIK</t>
-  </si>
-  <si>
-    <t>10 DE ABRIL</t>
-  </si>
-  <si>
     <t>PARADOR YBR125</t>
   </si>
   <si>
     <t>16 DE ABRIL</t>
   </si>
   <si>
-    <t xml:space="preserve">FILTRO DE GASOLINA CARTON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAPEMEX </t>
-  </si>
-  <si>
     <t>ARNES PRINCIPAL FT150</t>
   </si>
   <si>
@@ -220,9 +190,6 @@
     <t xml:space="preserve">MANUBRIO DE 3 PIEZAS </t>
   </si>
   <si>
-    <t>FILTROD E ACEITE FZ16</t>
-  </si>
-  <si>
     <t>ACIENTO DE 150Z</t>
   </si>
   <si>
@@ -233,6 +200,90 @@
   </si>
   <si>
     <t>02 DE MAYO</t>
+  </si>
+  <si>
+    <t>FILTRO DE AIRE XL150</t>
+  </si>
+  <si>
+    <t>MANDO IZQUIERDO DERECHO BOXER150</t>
+  </si>
+  <si>
+    <t>MANDO DERECHO DM150</t>
+  </si>
+  <si>
+    <t>RIND TRASERO FT150</t>
+  </si>
+  <si>
+    <t>RIND TRASERO DM200</t>
+  </si>
+  <si>
+    <t>RELEVADOR FT150</t>
+  </si>
+  <si>
+    <t>05 DE MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOGLES </t>
+  </si>
+  <si>
+    <t>BALERO 6300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO DE AIRE HONDA NAVI </t>
+  </si>
+  <si>
+    <t>CABEZA DE CILINDRO DS150</t>
+  </si>
+  <si>
+    <t>EJE DELANTERO DS150</t>
+  </si>
+  <si>
+    <t>RESORTE DE FT150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANGUERA DE FRENO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOGLES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPEJOS DE HONDA </t>
+  </si>
+  <si>
+    <t>CALABERA DE FT1125</t>
+  </si>
+  <si>
+    <t>EJE TRASERO DE FT150</t>
+  </si>
+  <si>
+    <t>22 DE ABRIL</t>
+  </si>
+  <si>
+    <t>01 DE MAYO</t>
+  </si>
+  <si>
+    <t>25  DE ABRIL</t>
+  </si>
+  <si>
+    <t>04 DE MAYO</t>
+  </si>
+  <si>
+    <t>07DE MAYO</t>
+  </si>
+  <si>
+    <t>07 DE MAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 DE MAYO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMBOR DE ATV 150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPEJOS DE ALERON </t>
+  </si>
+  <si>
+    <t>ACEITE MOTUL 7100 10W-40</t>
   </si>
 </sst>
 </file>
@@ -418,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -457,6 +508,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,10 +587,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>MANUBRIOFZ16</c:v>
+                  <c:v>GOGLES </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>NASAKI</c:v>
+                  <c:v>MERCADO LIBRE </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -556,7 +609,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="24"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -570,28 +623,55 @@
                   <c:v>12 DE DICIEMBRE-25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10 DE ABRIL</c:v>
+                  <c:v>16 DE ABRIL</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>16 DE ABRIL</c:v>
+                  <c:v>22 DE ABRIL</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>16 DE ABRIL</c:v>
+                  <c:v>25 DE ABRIL-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25 DE ABRIL-26</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25  DE ABRIL</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>01 DE MAYO</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>01 DE MAYO</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>02 DE MAYO</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>02 DE MAYO</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>04 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>22 DE ABRIL-26</c:v>
+                  <c:v>05 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>22 DE ABRIL-26</c:v>
+                  <c:v>05 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>25 DE ABRIL-26</c:v>
+                  <c:v>05 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>25 DE ABRIL-26</c:v>
+                  <c:v>05 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>25 DE ABRIL-26</c:v>
+                  <c:v>05 DE MAYO</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>05 DE MAYO</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>07DE MAYO</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -602,6 +682,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1699,7 +1782,9 @@
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -1995,14 +2080,12 @@
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>54</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C21" s="7"/>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -2015,12 +2098,14 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="9"/>
+        <v>75</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D22" s="22"/>
       <c r="E22" s="23" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
@@ -2033,14 +2118,14 @@
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
-        <v>57</v>
+      <c r="E23" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
@@ -2051,11 +2136,17 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="21"/>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="21" t="s">
+        <v>42</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -2066,10 +2157,16 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="21"/>
+      <c r="B25" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2079,11 +2176,17 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="21"/>
+    <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2094,10 +2197,16 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="B27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2108,10 +2217,16 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="10"/>
-      <c r="C28" s="19"/>
+      <c r="B28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2121,18 +2236,26 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="E29" s="21"/>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="B30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="G30" s="1"/>
@@ -2140,239 +2263,264 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="B31" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="B32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="7" t="s">
+      <c r="B33" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="1" t="s">
-        <v>44</v>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="1" t="s">
-        <v>44</v>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="7" t="s">
+      <c r="B35" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="1" t="s">
-        <v>47</v>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="7" t="s">
+      <c r="B36" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="1" t="s">
-        <v>47</v>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="9" t="s">
+      <c r="B37" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="21" t="s">
-        <v>47</v>
+      <c r="D37" s="29"/>
+      <c r="E37" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="21"/>
+      <c r="B38" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="7" t="s">
+      <c r="B39" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10" t="s">
+        <v>80</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="21"/>
+      <c r="B40" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" s="7" t="s">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="21"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="21" t="s">
-        <v>68</v>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" s="9" t="s">
+      <c r="B43" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="1"/>
-      <c r="E43" s="21"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10" t="s">
+        <v>80</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="G44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="B45" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="21"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="7" t="s">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10" t="s">
+        <v>82</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>2</v>
-      </c>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
     </row>
     <row r="49" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
@@ -2380,7 +2528,7 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="G49" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2398,7 +2546,7 @@
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="G51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -2406,42 +2554,54 @@
       <c r="C52" s="9"/>
       <c r="D52" s="18"/>
       <c r="E52" s="1"/>
-      <c r="G52" s="1"/>
+      <c r="G52" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="G53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
+      <c r="G55" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
+      <c r="G56" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="G57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="5"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1270C95B-320A-4236-88A9-2CCA2D22F42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB68C94-B273-4D22-A43D-C5243047A208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="88">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -151,27 +151,12 @@
     <t xml:space="preserve">PEDIDO MERCADO LIBRE </t>
   </si>
   <si>
-    <t>POSAPIE IZQUIERO DERECHO 250Z Y IZQUIERDO 250Z</t>
-  </si>
-  <si>
     <t>25 DE ABRIL-26</t>
   </si>
   <si>
-    <t>JUNTAS DE MOTOR FZ16</t>
-  </si>
-  <si>
-    <t>CAMARA 90-90-18</t>
-  </si>
-  <si>
-    <t>PEDAL DE CAMBIOS 125Z</t>
-  </si>
-  <si>
     <t>MANUBRIOFZ16</t>
   </si>
   <si>
-    <t>CHICOTED E CLUTH FT150</t>
-  </si>
-  <si>
     <t>PARADOR YBR125</t>
   </si>
   <si>
@@ -184,12 +169,6 @@
     <t>WAPEMEX</t>
   </si>
   <si>
-    <t>MANIJA IZQUIERDA BOXER 150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUBRIO DE 3 PIEZAS </t>
-  </si>
-  <si>
     <t>ACIENTO DE 150Z</t>
   </si>
   <si>
@@ -244,9 +223,6 @@
     <t xml:space="preserve">MANGUERA DE FRENO </t>
   </si>
   <si>
-    <t xml:space="preserve">GOOGLES </t>
-  </si>
-  <si>
     <t xml:space="preserve">ESPEJOS DE HONDA </t>
   </si>
   <si>
@@ -277,13 +253,43 @@
     <t xml:space="preserve">07 DE MAYO </t>
   </si>
   <si>
-    <t xml:space="preserve">TAMBOR DE ATV 150 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPEJOS DE ALERON </t>
-  </si>
-  <si>
     <t>ACEITE MOTUL 7100 10W-40</t>
+  </si>
+  <si>
+    <t>CADENA DE DISTRIBUCCION DS150</t>
+  </si>
+  <si>
+    <t>BARILLA DE FRENO DE DM200, FT150</t>
+  </si>
+  <si>
+    <t>BARARS DE DM200</t>
+  </si>
+  <si>
+    <t>PARADOR LATERAL 125Z</t>
+  </si>
+  <si>
+    <t>N ASAKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRELLA DEFT150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">POSAPIE DELANTERO FZ16 </t>
+  </si>
+  <si>
+    <t>PROMOTO</t>
+  </si>
+  <si>
+    <t>BALATA DELANTERO DM200 DISCO</t>
+  </si>
+  <si>
+    <t>NASAKIK</t>
+  </si>
+  <si>
+    <t>DISCO DE FRENO TRASERO 250Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOMBA DE FRENO TRASERO ATV </t>
   </si>
 </sst>
 </file>
@@ -496,6 +502,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -508,8 +516,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,9 +634,6 @@
                 <c:pt idx="8">
                   <c:v>22 DE ABRIL</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>25 DE ABRIL-26</c:v>
-                </c:pt>
                 <c:pt idx="10">
                   <c:v>25 DE ABRIL-26</c:v>
                 </c:pt>
@@ -638,9 +641,6 @@
                   <c:v>25  DE ABRIL</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>01 DE MAYO</c:v>
-                </c:pt>
-                <c:pt idx="13">
                   <c:v>01 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="14">
@@ -1759,11 +1759,11 @@
       <c r="B5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29"/>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1783,11 +1783,11 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+        <v>75</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="G6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1811,9 +1811,9 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1835,9 +1835,9 @@
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
       <c r="G8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1859,9 +1859,9 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
       <c r="G9" s="1" t="s">
         <v>9</v>
       </c>
@@ -1883,9 +1883,9 @@
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
       <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1902,9 +1902,9 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
@@ -1918,9 +1918,9 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
       <c r="G12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2080,12 +2080,12 @@
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -2098,14 +2098,14 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="23" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
@@ -2117,16 +2117,10 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="E23" s="1"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2137,15 +2131,13 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="9" t="s">
-        <v>44</v>
-      </c>
+      <c r="B24" s="9"/>
       <c r="C24" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -2157,15 +2149,13 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="B25" s="7"/>
       <c r="C25" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -2178,14 +2168,14 @@
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -2197,16 +2187,10 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="E27" s="1"/>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2218,14 +2202,14 @@
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
@@ -2237,12 +2221,8 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="1"/>
       <c r="E29" s="21"/>
       <c r="G29" s="1"/>
@@ -2250,12 +2230,8 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>5</v>
-      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="G30" s="1"/>
@@ -2264,14 +2240,14 @@
     </row>
     <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="19" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
@@ -2279,14 +2255,14 @@
     </row>
     <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B32" s="19" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
@@ -2294,14 +2270,14 @@
     </row>
     <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
@@ -2309,14 +2285,14 @@
     </row>
     <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B34" s="19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
@@ -2324,14 +2300,14 @@
     </row>
     <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B35" s="19" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
@@ -2339,29 +2315,29 @@
     </row>
     <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B36" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="28" t="s">
+      <c r="B37" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="29"/>
+      <c r="D37" s="25"/>
       <c r="E37" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
@@ -2369,14 +2345,14 @@
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B38" s="19" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C38" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
@@ -2384,14 +2360,14 @@
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B39" s="19" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
@@ -2399,132 +2375,140 @@
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B40" s="19" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="28" t="s">
+      <c r="B41" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="28" t="s">
+      <c r="B42" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="28" t="s">
+      <c r="B43" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="28" t="s">
+      <c r="B44" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="28" t="s">
+      <c r="B45" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="28" t="s">
+      <c r="B46" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="28" t="s">
+      <c r="B47" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
+      <c r="B48" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="D48" s="1"/>
     </row>
     <row r="49" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
+      <c r="B49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="G49" s="10" t="s">
@@ -2532,8 +2516,12 @@
       </c>
     </row>
     <row r="50" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
+      <c r="B50" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="G50" s="1" t="s">
@@ -2541,67 +2529,79 @@
       </c>
     </row>
     <row r="51" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
+      <c r="B51" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="G51" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
+      <c r="B52" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D52" s="18"/>
       <c r="E52" s="1"/>
       <c r="G52" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
+      <c r="B53" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
+      <c r="B54" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="G54" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
+      <c r="B55" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="G55" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="G56" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="G57" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="G57" s="1"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="5"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB68C94-B273-4D22-A43D-C5243047A208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58538252-F00E-4321-9898-1F3F3AF9B4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -118,24 +118,12 @@
     <t xml:space="preserve">14 DE OCTUBRE </t>
   </si>
   <si>
-    <t xml:space="preserve">CANDADO 520 </t>
-  </si>
-  <si>
     <t>7 DE NOVIEMBRE</t>
   </si>
   <si>
-    <t>MERCADO LIBRE</t>
-  </si>
-  <si>
     <t>FITRO DE AIRE HONDA WEBE 110</t>
   </si>
   <si>
-    <t>12 DE DICIEMBRE-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POSAPIE DE 250Z AMBOS </t>
-  </si>
-  <si>
     <t>Aceites</t>
   </si>
   <si>
@@ -145,114 +133,30 @@
     <t xml:space="preserve">PATITOS </t>
   </si>
   <si>
-    <t>ASAKI</t>
-  </si>
-  <si>
     <t xml:space="preserve">PEDIDO MERCADO LIBRE </t>
   </si>
   <si>
-    <t>25 DE ABRIL-26</t>
-  </si>
-  <si>
-    <t>MANUBRIOFZ16</t>
-  </si>
-  <si>
     <t>PARADOR YBR125</t>
   </si>
   <si>
-    <t>16 DE ABRIL</t>
-  </si>
-  <si>
-    <t>ARNES PRINCIPAL FT150</t>
-  </si>
-  <si>
     <t>WAPEMEX</t>
   </si>
   <si>
-    <t>ACIENTO DE 150Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POSAPIE UNIVERSALES </t>
-  </si>
-  <si>
-    <t>MANIJA IZQUIERDA FT150</t>
-  </si>
-  <si>
-    <t>02 DE MAYO</t>
-  </si>
-  <si>
-    <t>FILTRO DE AIRE XL150</t>
-  </si>
-  <si>
-    <t>MANDO IZQUIERDO DERECHO BOXER150</t>
-  </si>
-  <si>
     <t>MANDO DERECHO DM150</t>
   </si>
   <si>
-    <t>RIND TRASERO FT150</t>
-  </si>
-  <si>
     <t>RIND TRASERO DM200</t>
   </si>
   <si>
-    <t>RELEVADOR FT150</t>
-  </si>
-  <si>
-    <t>05 DE MAYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOGLES </t>
-  </si>
-  <si>
-    <t>BALERO 6300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO DE AIRE HONDA NAVI </t>
-  </si>
-  <si>
-    <t>CABEZA DE CILINDRO DS150</t>
-  </si>
-  <si>
-    <t>EJE DELANTERO DS150</t>
-  </si>
-  <si>
-    <t>RESORTE DE FT150</t>
-  </si>
-  <si>
     <t xml:space="preserve">MANGUERA DE FRENO </t>
   </si>
   <si>
     <t xml:space="preserve">ESPEJOS DE HONDA </t>
   </si>
   <si>
-    <t>CALABERA DE FT1125</t>
-  </si>
-  <si>
     <t>EJE TRASERO DE FT150</t>
   </si>
   <si>
-    <t>22 DE ABRIL</t>
-  </si>
-  <si>
-    <t>01 DE MAYO</t>
-  </si>
-  <si>
-    <t>25  DE ABRIL</t>
-  </si>
-  <si>
-    <t>04 DE MAYO</t>
-  </si>
-  <si>
-    <t>07DE MAYO</t>
-  </si>
-  <si>
-    <t>07 DE MAYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 DE MAYO </t>
-  </si>
-  <si>
     <t>ACEITE MOTUL 7100 10W-40</t>
   </si>
   <si>
@@ -290,6 +194,69 @@
   </si>
   <si>
     <t xml:space="preserve">BOMBA DE FRENO TRASERO ATV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDA PARA CUBRIR MOTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE PARA ESPEJOS </t>
+  </si>
+  <si>
+    <t>CHCIOCTE CDE VELOCIMETRO WS150</t>
+  </si>
+  <si>
+    <t>18 DE MAYO</t>
+  </si>
+  <si>
+    <t>BALERO 6004</t>
+  </si>
+  <si>
+    <t>DIRECCIONAL TRASERA WS175 SPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMORTIGUADOR DE VENTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANDOM DERECHO ROKEMAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPRORADORAS DE LUPA </t>
+  </si>
+  <si>
+    <t>PATITOS</t>
+  </si>
+  <si>
+    <t>16 DE ABRIL-26</t>
+  </si>
+  <si>
+    <t>22 DEABRIL</t>
+  </si>
+  <si>
+    <t>05 DE MAYO-26</t>
+  </si>
+  <si>
+    <t>14 DE MAYO-26</t>
+  </si>
+  <si>
+    <t>22 DE MAYO</t>
+  </si>
+  <si>
+    <t>BALATA DE DISCO DS150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARO DE FT150 </t>
+  </si>
+  <si>
+    <t>camara 120-90-10</t>
+  </si>
+  <si>
+    <t>nasaki</t>
+  </si>
+  <si>
+    <t>23 DE MAYO-26</t>
+  </si>
+  <si>
+    <t>23 DE MAYO+-26</t>
   </si>
 </sst>
 </file>
@@ -494,16 +461,16 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -593,10 +560,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>GOGLES </c:v>
+                  <c:v>FARO DE FT150 </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>MERCADO LIBRE </c:v>
+                  <c:v>NASAKI</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -615,7 +582,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="26"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -626,52 +593,58 @@
                   <c:v>7 DE NOVIEMBRE</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12 DE DICIEMBRE-25</c:v>
+                  <c:v>16 DE ABRIL-26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22 DEABRIL</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16 DE ABRIL</c:v>
+                  <c:v>05 DE MAYO-26</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>22 DE ABRIL</c:v>
+                <c:pt idx="9">
+                  <c:v>14 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25 DE ABRIL-26</c:v>
+                  <c:v>14 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25  DE ABRIL</c:v>
+                  <c:v>14 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>01 DE MAYO</c:v>
+                  <c:v>14 DE MAYO-26</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>02 DE MAYO</c:v>
+                  <c:v>14 DE MAYO-26</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>14 DE MAYO-26</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>02 DE MAYO</c:v>
+                  <c:v>18 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>04 DE MAYO</c:v>
+                  <c:v>22 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>05 DE MAYO</c:v>
+                  <c:v>22 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>05 DE MAYO</c:v>
+                  <c:v>22 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>05 DE MAYO</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>05 DE MAYO</c:v>
+                  <c:v>22 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>05 DE MAYO</c:v>
+                  <c:v>23 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>05 DE MAYO</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>07DE MAYO</c:v>
+                  <c:v>23 DE MAYO+-26</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -682,9 +655,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1756,11 +1726,11 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="20" t="s">
-        <v>36</v>
+      <c r="B5" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="29"/>
@@ -1783,7 +1753,7 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -1996,7 +1966,7 @@
         <v>29</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2013,7 +1983,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1"/>
       <c r="I17" s="1"/>
@@ -2026,10 +1996,10 @@
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -2044,14 +2014,12 @@
     </row>
     <row r="19" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>32</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C19" s="7"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="1"/>
@@ -2064,11 +2032,15 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -2080,12 +2052,14 @@
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -2098,15 +2072,13 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23" t="s">
-        <v>68</v>
-      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -2116,11 +2088,17 @@
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="23" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="1"/>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="24" t="s">
+        <v>69</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2130,14 +2108,16 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="9"/>
-      <c r="C24" s="9" t="s">
+    <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="21" t="s">
-        <v>41</v>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -2149,13 +2129,15 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="1" t="s">
-        <v>70</v>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -2167,14 +2149,14 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="1" t="s">
+      <c r="B26" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="1"/>
@@ -2186,11 +2168,17 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
     </row>
-    <row r="27" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2201,15 +2189,15 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
+      <c r="B28" s="18" t="s">
         <v>50</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
@@ -2220,381 +2208,312 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="21"/>
+    <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="B30" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>46</v>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>2</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="19" t="s">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="19" t="s">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>2</v>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>37</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="19" t="s">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>2</v>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="D36" s="10"/>
-      <c r="E36" s="10" t="s">
-        <v>57</v>
-      </c>
+      <c r="E36" s="10"/>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="24" t="s">
+      <c r="B37" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="10" t="s">
-        <v>57</v>
+      <c r="D37" s="20"/>
+      <c r="E37" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10" t="s">
-        <v>57</v>
+      <c r="B38" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10" t="s">
-        <v>72</v>
-      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10" t="s">
-        <v>73</v>
-      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10" t="s">
-        <v>73</v>
-      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10" t="s">
-        <v>72</v>
-      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
       <c r="G42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10" t="s">
-        <v>72</v>
-      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
       <c r="G43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10" t="s">
-        <v>73</v>
-      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
       <c r="G44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10" t="s">
-        <v>73</v>
-      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
       <c r="G45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10" t="s">
-        <v>73</v>
-      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
       <c r="G46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10" t="s">
-        <v>74</v>
-      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
       <c r="G47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="1"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="25"/>
     </row>
     <row r="49" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
       <c r="G49" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
       <c r="G50" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
       <c r="G51" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="8"/>
+      <c r="G52" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="G53" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="1"/>
-      <c r="G52" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="G53" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
     <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="G54" s="1"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="G54" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="G55" s="1"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="G55" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="G56" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="5"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58538252-F00E-4321-9898-1F3F3AF9B4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F52043E-11B5-4484-90A1-DE420ED9E268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -160,39 +160,6 @@
     <t>ACEITE MOTUL 7100 10W-40</t>
   </si>
   <si>
-    <t>CADENA DE DISTRIBUCCION DS150</t>
-  </si>
-  <si>
-    <t>BARILLA DE FRENO DE DM200, FT150</t>
-  </si>
-  <si>
-    <t>BARARS DE DM200</t>
-  </si>
-  <si>
-    <t>PARADOR LATERAL 125Z</t>
-  </si>
-  <si>
-    <t>N ASAKI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRELLA DEFT150 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">POSAPIE DELANTERO FZ16 </t>
-  </si>
-  <si>
-    <t>PROMOTO</t>
-  </si>
-  <si>
-    <t>BALATA DELANTERO DM200 DISCO</t>
-  </si>
-  <si>
-    <t>NASAKIK</t>
-  </si>
-  <si>
-    <t>DISCO DE FRENO TRASERO 250Z</t>
-  </si>
-  <si>
     <t xml:space="preserve">BOMBA DE FRENO TRASERO ATV </t>
   </si>
   <si>
@@ -235,9 +202,6 @@
     <t>05 DE MAYO-26</t>
   </si>
   <si>
-    <t>14 DE MAYO-26</t>
-  </si>
-  <si>
     <t>22 DE MAYO</t>
   </si>
   <si>
@@ -257,6 +221,9 @@
   </si>
   <si>
     <t>23 DE MAYO+-26</t>
+  </si>
+  <si>
+    <t>CHICOTE DE CLTUH 150Z</t>
   </si>
 </sst>
 </file>
@@ -560,7 +527,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>FARO DE FT150 </c:v>
+                  <c:v>CHICOTE DE CLTUH 150Z</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>NASAKI</c:v>
@@ -600,30 +567,6 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>05 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>14 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>14 DE MAYO-26</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>18 DE MAYO</c:v>
@@ -1996,7 +1939,7 @@
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>5</v>
@@ -2019,7 +1962,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="1"/>
@@ -2039,7 +1982,7 @@
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
@@ -2059,7 +2002,7 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -2089,16 +2032,10 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>2</v>
-      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="10"/>
-      <c r="E23" s="24" t="s">
-        <v>69</v>
-      </c>
+      <c r="E23" s="24"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2109,16 +2046,10 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>2</v>
-      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E24" s="10"/>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -2129,16 +2060,10 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>2</v>
-      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E25" s="10"/>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2149,16 +2074,10 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>48</v>
-      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E26" s="10"/>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2169,16 +2088,10 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>2</v>
-      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E27" s="10"/>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2189,16 +2102,10 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>51</v>
-      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E28" s="10"/>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2209,45 +2116,33 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>53</v>
-      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
       <c r="D29" s="10"/>
-      <c r="E29" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E29" s="10"/>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>2</v>
-      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="10"/>
-      <c r="E30" s="10" t="s">
-        <v>69</v>
-      </c>
+      <c r="E30" s="10"/>
       <c r="G30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
@@ -2255,14 +2150,14 @@
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C32" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
@@ -2270,14 +2165,14 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="22" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C33" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
@@ -2285,14 +2180,14 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="22" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C34" s="22" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
@@ -2300,14 +2195,14 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
@@ -2315,7 +2210,7 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>5</v>
@@ -2328,14 +2223,14 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="8" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
@@ -2343,22 +2238,26 @@
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
+      <c r="B39" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="G39" s="1"/>
@@ -2485,7 +2384,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="G53" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2494,7 +2393,7 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="G54" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2503,7 +2402,7 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="G55" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
@@ -2512,7 +2411,7 @@
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F52043E-11B5-4484-90A1-DE420ED9E268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D887A3-33DA-4884-AB16-7696A997F34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -169,18 +169,6 @@
     <t xml:space="preserve">BASE PARA ESPEJOS </t>
   </si>
   <si>
-    <t>CHCIOCTE CDE VELOCIMETRO WS150</t>
-  </si>
-  <si>
-    <t>18 DE MAYO</t>
-  </si>
-  <si>
-    <t>BALERO 6004</t>
-  </si>
-  <si>
-    <t>DIRECCIONAL TRASERA WS175 SPORT</t>
-  </si>
-  <si>
     <t xml:space="preserve">AMORTIGUADOR DE VENTO </t>
   </si>
   <si>
@@ -205,12 +193,6 @@
     <t>22 DE MAYO</t>
   </si>
   <si>
-    <t>BALATA DE DISCO DS150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARO DE FT150 </t>
-  </si>
-  <si>
     <t>camara 120-90-10</t>
   </si>
   <si>
@@ -224,6 +206,18 @@
   </si>
   <si>
     <t>CHICOTE DE CLTUH 150Z</t>
+  </si>
+  <si>
+    <t>SALPICADERA DELANTERA ft150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILENCIADOR </t>
+  </si>
+  <si>
+    <t>LLANTA 110-80-17</t>
+  </si>
+  <si>
+    <t>LLANTA 110-70-17</t>
   </si>
 </sst>
 </file>
@@ -527,10 +521,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>CHICOTE DE CLTUH 150Z</c:v>
+                  <c:v>SALPICADERA DELANTERA ft150</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>NASAKI</c:v>
+                  <c:v>nasaki</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -567,12 +561,6 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>05 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18 DE MAYO</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>22 DE MAYO</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>22 DE MAYO</c:v>
@@ -1939,7 +1927,7 @@
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>5</v>
@@ -1962,7 +1950,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="1"/>
@@ -1982,7 +1970,7 @@
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
@@ -2002,7 +1990,7 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -2134,45 +2122,29 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>2</v>
-      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
-        <v>48</v>
-      </c>
+      <c r="E31" s="10"/>
       <c r="G31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>2</v>
-      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
       <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
-        <v>58</v>
-      </c>
+      <c r="E32" s="10"/>
       <c r="G32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>2</v>
-      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
@@ -2180,29 +2152,27 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="22" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C34" s="22" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="22" t="s">
-        <v>59</v>
-      </c>
+      <c r="B35" s="22"/>
       <c r="C35" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
@@ -2210,7 +2180,7 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>5</v>
@@ -2222,15 +2192,11 @@
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="20"/>
       <c r="E37" s="8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
@@ -2238,14 +2204,14 @@
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
@@ -2253,7 +2219,7 @@
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>2</v>
@@ -2265,8 +2231,12 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
+      <c r="B40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="G40" s="1"/>
@@ -2274,8 +2244,12 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>5</v>
+      </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="G41" s="1"/>
@@ -2283,7 +2257,9 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="9"/>
+      <c r="B42" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="C42" s="9"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2292,7 +2268,9 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
+      <c r="B43" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -2411,7 +2389,7 @@
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D887A3-33DA-4884-AB16-7696A997F34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A559982-9748-469B-A68D-8B2259A3FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -142,82 +142,61 @@
     <t>WAPEMEX</t>
   </si>
   <si>
-    <t>MANDO DERECHO DM150</t>
-  </si>
-  <si>
-    <t>RIND TRASERO DM200</t>
-  </si>
-  <si>
     <t xml:space="preserve">MANGUERA DE FRENO </t>
   </si>
   <si>
-    <t xml:space="preserve">ESPEJOS DE HONDA </t>
-  </si>
-  <si>
     <t>EJE TRASERO DE FT150</t>
   </si>
   <si>
-    <t>ACEITE MOTUL 7100 10W-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOMBA DE FRENO TRASERO ATV </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNDA PARA CUBRIR MOTO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASE PARA ESPEJOS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMORTIGUADOR DE VENTO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANDOM DERECHO ROKEMAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPRORADORAS DE LUPA </t>
-  </si>
-  <si>
     <t>PATITOS</t>
   </si>
   <si>
     <t>16 DE ABRIL-26</t>
   </si>
   <si>
-    <t>22 DEABRIL</t>
-  </si>
-  <si>
     <t>05 DE MAYO-26</t>
   </si>
   <si>
-    <t>22 DE MAYO</t>
-  </si>
-  <si>
-    <t>camara 120-90-10</t>
-  </si>
-  <si>
-    <t>nasaki</t>
-  </si>
-  <si>
-    <t>23 DE MAYO-26</t>
-  </si>
-  <si>
-    <t>23 DE MAYO+-26</t>
-  </si>
-  <si>
-    <t>CHICOTE DE CLTUH 150Z</t>
-  </si>
-  <si>
-    <t>SALPICADERA DELANTERA ft150</t>
-  </si>
-  <si>
     <t xml:space="preserve">SILENCIADOR </t>
   </si>
   <si>
-    <t>LLANTA 110-80-17</t>
-  </si>
-  <si>
-    <t>LLANTA 110-70-17</t>
+    <t xml:space="preserve">MANDO DERECHO ROKETMAN </t>
+  </si>
+  <si>
+    <t>22 DE MMAYO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TENSOR DE CADENA DS150 DISTRIBUCCION </t>
+  </si>
+  <si>
+    <t>16 DE JUNIO-26</t>
+  </si>
+  <si>
+    <t>CHICOTE DE ACELERADOR YBR125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSPEMEX </t>
+  </si>
+  <si>
+    <t>VALVULAS DE 250Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORTADOR DE DISTRIBUCCION UNIVERSAL </t>
+  </si>
+  <si>
+    <t>ACEITE MOTUL 5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICOTE DE ACELRADOR 150Z 170Z 125Z </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGADOR DE BATERIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOGLES NEGROS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTAPALCA CON DIRECCIONALES </t>
   </si>
 </sst>
 </file>
@@ -521,10 +500,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>SALPICADERA DELANTERA ft150</c:v>
+                  <c:v>CHICOTE DE ACELRADOR 150Z 170Z 125Z </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>nasaki</c:v>
+                  <c:v>NASAKI</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -543,7 +522,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="25"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -556,26 +535,23 @@
                 <c:pt idx="5">
                   <c:v>16 DE ABRIL-26</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>22 DEABRIL</c:v>
-                </c:pt>
                 <c:pt idx="7">
                   <c:v>05 DE MAYO-26</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>22 DE MAYO</c:v>
+                <c:pt idx="8">
+                  <c:v>22 DE MMAYO</c:v>
                 </c:pt>
-                <c:pt idx="20">
-                  <c:v>22 DE MAYO</c:v>
+                <c:pt idx="10">
+                  <c:v>16 DE JUNIO-26</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>22 DE MAYO</c:v>
+                <c:pt idx="11">
+                  <c:v>16 DE JUNIO-26</c:v>
                 </c:pt>
-                <c:pt idx="23">
-                  <c:v>23 DE MAYO-26</c:v>
+                <c:pt idx="12">
+                  <c:v>16 DE JUNIO-26</c:v>
                 </c:pt>
-                <c:pt idx="24">
-                  <c:v>23 DE MAYO+-26</c:v>
+                <c:pt idx="13">
+                  <c:v>16 DE JUNIO-26</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1684,7 +1660,7 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -1927,7 +1903,7 @@
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>5</v>
@@ -1950,7 +1926,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="1"/>
@@ -1963,15 +1939,13 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="E20" s="1"/>
       <c r="G20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1990,7 +1964,7 @@
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="15" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
@@ -2003,13 +1977,15 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D22" s="20"/>
-      <c r="E22" s="21"/>
+      <c r="E22" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -2020,8 +1996,12 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
+      <c r="B23" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>5</v>
+      </c>
       <c r="D23" s="10"/>
       <c r="E23" s="24"/>
       <c r="G23" s="1"/>
@@ -2034,10 +2014,16 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>2</v>
+      </c>
       <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="E24" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -2048,10 +2034,16 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="B25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>49</v>
+      </c>
       <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="E25" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -2062,10 +2054,16 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
+      <c r="B26" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>2</v>
+      </c>
       <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="E26" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -2076,10 +2074,16 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
+      <c r="B27" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>2</v>
+      </c>
       <c r="D27" s="23"/>
-      <c r="E27" s="10"/>
+      <c r="E27" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2090,8 +2094,12 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
+      <c r="B28" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>2</v>
+      </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="G28" s="1"/>
@@ -2143,48 +2151,32 @@
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
       <c r="D33" s="10"/>
-      <c r="E33" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="E33" s="10"/>
       <c r="G33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>37</v>
-      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="E34" s="10"/>
       <c r="G34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="22"/>
-      <c r="C35" s="22" t="s">
-        <v>2</v>
-      </c>
+      <c r="C35" s="22"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="10" t="s">
-        <v>54</v>
-      </c>
+      <c r="E35" s="10"/>
       <c r="G35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>5</v>
-      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
       <c r="G36" s="1"/>
@@ -2195,35 +2187,23 @@
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="20"/>
-      <c r="E37" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="E37" s="8"/>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="E38" s="8"/>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="G39" s="1"/>
@@ -2231,12 +2211,8 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="G40" s="1"/>
@@ -2244,12 +2220,8 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>5</v>
-      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="G41" s="1"/>
@@ -2257,9 +2229,7 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="9" t="s">
-        <v>62</v>
-      </c>
+      <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2268,9 +2238,7 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="9" t="s">
-        <v>63</v>
-      </c>
+      <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -2344,7 +2312,7 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="G51" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -2353,7 +2321,7 @@
       <c r="D52" s="20"/>
       <c r="E52" s="8"/>
       <c r="G52" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2362,7 +2330,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="G53" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2370,27 +2338,21 @@
       <c r="C54" s="7"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="G54" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="G54" s="1"/>
     </row>
     <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="G55" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="G55" s="1"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="G56" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="G56" s="1"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="5"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A559982-9748-469B-A68D-8B2259A3FBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1316EF58-96E2-447C-B08D-321A066D9AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -139,12 +139,6 @@
     <t>PARADOR YBR125</t>
   </si>
   <si>
-    <t>WAPEMEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUERA DE FRENO </t>
-  </si>
-  <si>
     <t>EJE TRASERO DE FT150</t>
   </si>
   <si>
@@ -154,42 +148,12 @@
     <t>16 DE ABRIL-26</t>
   </si>
   <si>
-    <t>05 DE MAYO-26</t>
-  </si>
-  <si>
     <t xml:space="preserve">SILENCIADOR </t>
   </si>
   <si>
-    <t xml:space="preserve">MANDO DERECHO ROKETMAN </t>
-  </si>
-  <si>
-    <t>22 DE MMAYO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TENSOR DE CADENA DS150 DISTRIBUCCION </t>
-  </si>
-  <si>
-    <t>16 DE JUNIO-26</t>
-  </si>
-  <si>
-    <t>CHICOTE DE ACELERADOR YBR125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSPEMEX </t>
-  </si>
-  <si>
-    <t>VALVULAS DE 250Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORTADOR DE DISTRIBUCCION UNIVERSAL </t>
-  </si>
-  <si>
     <t>ACEITE MOTUL 5000</t>
   </si>
   <si>
-    <t xml:space="preserve">CHICOTE DE ACELRADOR 150Z 170Z 125Z </t>
-  </si>
-  <si>
     <t xml:space="preserve">CARGADOR DE BATERIA </t>
   </si>
   <si>
@@ -197,6 +161,48 @@
   </si>
   <si>
     <t xml:space="preserve">PORTAPALCA CON DIRECCIONALES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCHA CARGO </t>
+  </si>
+  <si>
+    <t>RESBALON DE CENTRIFUJO DS150</t>
+  </si>
+  <si>
+    <t>RODILLOS DE CENTRIFUJO DS150</t>
+  </si>
+  <si>
+    <t>MANIJA IZQUIERDA DS150</t>
+  </si>
+  <si>
+    <t>MANIJA IZQUIEERDA WS150 SPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICOTED DE ACELERADOR DS150 , </t>
+  </si>
+  <si>
+    <t>CHICOTE DE ACELERADOR BOXER 150</t>
+  </si>
+  <si>
+    <t>TAPON DE GASOLINA FT150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWUITH INIVERSAL 4 PUNTAS </t>
+  </si>
+  <si>
+    <t>FILTRO DE AIRE FT125</t>
+  </si>
+  <si>
+    <t>PEDAL DE ARRANQUE FT180 RT200</t>
+  </si>
+  <si>
+    <t>CAMARA 120-80-18</t>
+  </si>
+  <si>
+    <t>01 DE JULIO-26</t>
+  </si>
+  <si>
+    <t>02 DE JULIO</t>
   </si>
 </sst>
 </file>
@@ -500,7 +506,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>CHICOTE DE ACELRADOR 150Z 170Z 125Z </c:v>
+                  <c:v>CAMARA 120-80-18</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>NASAKI</c:v>
@@ -522,7 +528,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -535,23 +541,26 @@
                 <c:pt idx="5">
                   <c:v>16 DE ABRIL-26</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>05 DE MAYO-26</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>22 DE MMAYO</c:v>
+                <c:pt idx="9">
+                  <c:v>01 DE JULIO-26</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16 DE JUNIO-26</c:v>
+                  <c:v>01 DE JULIO-26</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>16 DE JUNIO-26</c:v>
+                  <c:v>01 DE JULIO-26</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16 DE JUNIO-26</c:v>
+                  <c:v>01 DE JULIO-26</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>16 DE JUNIO-26</c:v>
+                  <c:v>01 DE JULIO-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>02 DE JULIO</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>02 DE JULIO</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1660,7 +1669,7 @@
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -1903,7 +1912,7 @@
     </row>
     <row r="18" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>5</v>
@@ -1926,7 +1935,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1"/>
       <c r="I19" s="1"/>
@@ -1939,7 +1948,7 @@
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>2</v>
@@ -1957,15 +1966,13 @@
     </row>
     <row r="21" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="15" t="s">
-        <v>42</v>
-      </c>
+      <c r="E21" s="15"/>
       <c r="G21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1977,15 +1984,11 @@
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>37</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C22" s="9"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="21" t="s">
-        <v>45</v>
-      </c>
+      <c r="E22" s="21"/>
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1997,13 +2000,15 @@
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="24"/>
+      <c r="E23" s="24" t="s">
+        <v>57</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G24" s="1"/>
       <c r="I24" s="1"/>
@@ -2038,11 +2043,11 @@
         <v>48</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
@@ -2055,14 +2060,14 @@
     </row>
     <row r="26" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G26" s="1"/>
       <c r="I26" s="1"/>
@@ -2075,14 +2080,14 @@
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G27" s="1"/>
       <c r="I27" s="1"/>
@@ -2095,13 +2100,15 @@
     </row>
     <row r="28" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="E28" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2112,17 +2119,27 @@
       <c r="P28" s="1"/>
     </row>
     <row r="29" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
+      <c r="B29" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>2</v>
+      </c>
       <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="E29" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="B30" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10"/>
       <c r="G30" s="1"/>
@@ -2130,8 +2147,12 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>2</v>
+      </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
       <c r="G31" s="1"/>
@@ -2139,8 +2160,12 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
+      <c r="B32" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>2</v>
+      </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
       <c r="G32" s="1"/>
@@ -2148,8 +2173,12 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
+      <c r="B33" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>2</v>
+      </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="G33" s="1"/>
@@ -2312,7 +2341,7 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="G51" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
@@ -2321,7 +2350,7 @@
       <c r="D52" s="20"/>
       <c r="E52" s="8"/>
       <c r="G52" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2330,7 +2359,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="G53" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1316EF58-96E2-447C-B08D-321A066D9AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB09123-9E1D-44F5-884C-F73FBDB3B8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -203,6 +203,36 @@
   </si>
   <si>
     <t>02 DE JULIO</t>
+  </si>
+  <si>
+    <t>TAPAS LATERALES FT150 NEGRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PILA 12N7 3B </t>
+  </si>
+  <si>
+    <t>N ASAKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHICOTE DE FRENO DELANTERO FT150 </t>
+  </si>
+  <si>
+    <t>PEDAL DE CAMBIOS 250Z</t>
+  </si>
+  <si>
+    <t>MANDO IZQUIERDO DERECHO FT150</t>
+  </si>
+  <si>
+    <t>09 DE JULIO</t>
+  </si>
+  <si>
+    <t>RED DE ACIENTO WS150</t>
+  </si>
+  <si>
+    <t>RED DE ACIENTO DS150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILENCIADORES </t>
   </si>
 </sst>
 </file>
@@ -506,7 +536,7 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>CAMARA 120-80-18</c:v>
+                  <c:v>RED DE ACIENTO DS150</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>NASAKI</c:v>
@@ -528,7 +558,7 @@
             <c:strRef>
               <c:f>Hoja1!$E$14:$E$39</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>FECHA </c:v>
                 </c:pt>
@@ -562,6 +592,18 @@
                 <c:pt idx="15">
                   <c:v>02 DE JULIO</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>09 DE JULIO</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>09 DE JULIO</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>09 DE JULIO</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>09 DE JULIO</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
@@ -571,6 +613,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2186,8 +2231,12 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>2</v>
+      </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
       <c r="G34" s="1"/>
@@ -2195,8 +2244,12 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
+      <c r="B35" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>61</v>
+      </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="G35" s="1"/>
@@ -2204,55 +2257,91 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
+      <c r="B36" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>2</v>
+      </c>
       <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
+      <c r="E36" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
+      <c r="B37" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D37" s="20"/>
-      <c r="E37" s="8"/>
+      <c r="E37" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
+      <c r="B38" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+      <c r="E38" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
+      <c r="B39" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
+      <c r="E39" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
+      <c r="B40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>2</v>
+      </c>
       <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="G41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -2367,7 +2456,9 @@
       <c r="C54" s="7"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="G54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="55" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B55" s="7"/>

--- a/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
+++ b/cosas por pedir/LISTA DE LOS PEDIDOS DE REFACCIONARIA MOTOZOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\cosas por pedir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB09123-9E1D-44F5-884C-F73FBDB3B8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB67EA0-6984-4F62-B66C-B5C31D472A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t xml:space="preserve">LISTA DE PEDIDO SEMANA 15 DE ABRIL </t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t xml:space="preserve">SILENCIADORES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASATAS DE CLUTH PARA LA 250Z </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASTAS DE CLUTH CROSMAX 250 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALARMA </t>
   </si>
 </sst>
 </file>
@@ -2347,7 +2356,9 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="9"/>
+      <c r="B42" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="C42" s="9"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -2356,7 +2367,9 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
+      <c r="B43" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -2465,7 +2478,9 @@
       <c r="C55" s="7"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="G55" s="1"/>
+      <c r="G55" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="5"/>
